--- a/3.-DOCUMENTACION/6. Matrices/Cronograma_Mesapass.xlsx
+++ b/3.-DOCUMENTACION/6. Matrices/Cronograma_Mesapass.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="87">
   <si>
     <t>Macro actividades</t>
   </si>
@@ -186,13 +187,112 @@
   </si>
   <si>
     <t>Sistema implementado y capacitado</t>
+  </si>
+  <si>
+    <t>Identificación y documentación de procesos del negocio</t>
+  </si>
+  <si>
+    <t>Diseño de arquitectura y diagramas BPMN</t>
+  </si>
+  <si>
+    <t>Desarrollo del sistema QR y control de consumos</t>
+  </si>
+  <si>
+    <t>Desarrollo del módulo de reportes y facturación</t>
+  </si>
+  <si>
+    <t>Implementación, capacitación y entrega final</t>
+  </si>
+  <si>
+    <t>CAMPO</t>
+  </si>
+  <si>
+    <t>DETALLE</t>
+  </si>
+  <si>
+    <t>No. Proyecto</t>
+  </si>
+  <si>
+    <t>MESAPASS-2026-001</t>
+  </si>
+  <si>
+    <t>No. Expediente Interno</t>
+  </si>
+  <si>
+    <t>MP-2026-01</t>
+  </si>
+  <si>
+    <t>No. Recomendación</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>Unidad Responsable</t>
+  </si>
+  <si>
+    <t>Equipo de Desarrollo MESAPASS</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>En proceso de desarrollo</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>Análisis, Diseño y Desarrollo</t>
+  </si>
+  <si>
+    <t>Duración</t>
+  </si>
+  <si>
+    <t>12 meses</t>
+  </si>
+  <si>
+    <t>Mes Inicio</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>PLANIFICACIÓN</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN DE HITOS</t>
+  </si>
+  <si>
+    <t>Requerimientos del sistema identificados</t>
+  </si>
+  <si>
+    <t>Procesos del negocio documentados</t>
+  </si>
+  <si>
+    <t>Arquitectura del sistema aprobada</t>
+  </si>
+  <si>
+    <t>Gestión de empresas y empleados completada</t>
+  </si>
+  <si>
+    <t>Sistema QR y consumos implementado</t>
+  </si>
+  <si>
+    <t>Reportes y facturación generados correctamente</t>
+  </si>
+  <si>
+    <t>Pruebas funcionales aprobadas</t>
+  </si>
+  <si>
+    <t>Cierre formal del proyecto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +303,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -256,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -267,6 +375,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -948,4 +1060,457 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:P32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.4">
+      <c r="E2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="D14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D19" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="D27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="D28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="D29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="D30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>